--- a/data/raw/data_raw_treatments.xlsx
+++ b/data/raw/data_raw_treatments.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816B5B49-D71B-493C-BD65-B814BD66D95E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10AAD65-D8FB-4429-839B-DD4CD42C62CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="-9210" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SWMREC" sheetId="1" r:id="rId1"/>
@@ -70,10 +70,10 @@
     <t>unseeded</t>
   </si>
   <si>
-    <t>species_pool</t>
+    <t>herbicide</t>
   </si>
   <si>
-    <t>herbicide</t>
+    <t>seeded_pool</t>
   </si>
 </sst>
 </file>
@@ -439,10 +439,10 @@
         <v>13</v>
       </c>
       <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
         <v>17</v>
-      </c>
-      <c r="F1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -1678,10 +1678,10 @@
         <v>13</v>
       </c>
       <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
         <v>17</v>
-      </c>
-      <c r="F1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2914,10 +2914,10 @@
         <v>13</v>
       </c>
       <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
         <v>17</v>
-      </c>
-      <c r="F1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">

--- a/data/raw/data_raw_treatments.xlsx
+++ b/data/raw/data_raw_treatments.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10AAD65-D8FB-4429-839B-DD4CD42C62CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E2720D-4047-4F6D-B541-CAFE101A4A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SWMREC" sheetId="1" r:id="rId1"/>
@@ -2898,6 +2898,7 @@
     <col min="2" max="2" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
